--- a/tests/fixtures/manual_spill_cache/copy_overlap.xlsx
+++ b/tests/fixtures/manual_spill_cache/copy_overlap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\pyOpenVBA\tests\fixtures\manual_spill_cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D6AF428-5107-4553-9005-ABE5AE6B02FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03049CE0-35CB-452D-AE0D-0B424F66D9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="7200" windowHeight="4545" xr2:uid="{2BABF28D-8C2D-4337-A0C9-32A7A8E875AF}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="7200" windowHeight="4545" xr2:uid="{31610634-3DD3-4F8B-B804-9B3B336CEA24}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -504,7 +504,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09FF5E0C-D814-40D1-A98C-C135A0AB20AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1DCEBD4-D136-463F-A2BA-2322E315A694}">
   <dimension ref="B2:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -524,7 +524,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0B62C57-156D-4805-94F2-32BD38A2ED8A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45B34DD6-FD9A-49BA-970B-CD5B0DD8180A}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
